--- a/机会命运卡牌总表.xlsx
+++ b/机会命运卡牌总表.xlsx
@@ -479,7 +479,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="48" customWidth="1" min="5" max="5"/>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>v5 邪恶版</t>
+          <t>v6 邪恶版</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>你举报同桌玩家偷税，税务局发举报奖金</t>
+          <t>你在瑞士的匿名账户被发现，你抢先举报同桌开曼账户的同行，瑞银发洗钱举报奖金</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>v5 邪恶版</t>
+          <t>v6 邪恶版</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>你冒充税务稽查员上门「查账」</t>
+          <t>你在巴拿马注册了空壳公司，冒充税务稽查员上门「查账」</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>v5 邪恶版</t>
+          <t>v6 邪恶版</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>你在赌场出千被荷官发现——但荷官是你发小</t>
+          <t>你在澳门赌场出千被荷官发现——但荷官是你发小</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>v5 邪恶版</t>
+          <t>v6 邪恶版</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>你把假地图卖给刚要出发的旅行团</t>
+          <t>你在撒哈拉把假罗盘卖给刚要进沙漠的旅行团</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>v5 邪恶版</t>
+          <t>v6 邪恶版</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>你倒卖限量球鞋，黄牛圈为你封神</t>
+          <t>你在米兰倒卖限量球鞋，黄牛圈为你封神</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>v5 邪恶版</t>
+          <t>v6 邪恶版</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>你买通裁判，你押的队「赢了」</t>
+          <t>你买通了马赛的裁判，你押的队「赢了」世界杯</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>v5 邪恶版</t>
+          <t>v6 邪恶版</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>你偷了隔壁玩家的登机牌，占了头等舱</t>
+          <t>你在伊斯坦布尔机场偷了隔壁玩家的登机牌，占了头等舱</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>v5 邪恶版</t>
+          <t>v6 邪恶版</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>你给对手的咖啡里下泻药，拍卖会上他狂奔离席</t>
+          <t>你在迪拜拍卖会前给对手的阿拉伯咖啡里下了泻药</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>v5 邪恶版</t>
+          <t>v6 邪恶版</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>你卖「防雷符」给富豪，当天下雨他就信了</t>
+          <t>你在里约把「防抢劫符」卖给富豪，当晚贫民窟枪一响他就信了</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>v5 邪恶版</t>
+          <t>v6 邪恶版</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>你在保险公司给你最贵的房投了灾险，然后隔壁「不小心」着火了</t>
+          <t>你在伦敦给你最贵的房产投了灾险，然后隔壁「不小心」着火了</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>v5 邪恶版</t>
+          <t>v6 邪恶版</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>你开了一家「监狱代购」，垄断了铁窗外的外卖</t>
+          <t>你在莫斯科开「监狱代购」，垄断了西伯利亚铁窗外的外卖</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>v5 邪恶版</t>
+          <t>v6 邪恶版</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>你仿冒名牌包卖给旅游团</t>
+          <t>你在广州仿冒名牌包卖给欧洲旅游团</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>v5 邪恶版</t>
+          <t>v6 邪恶版</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>你把游戏说明书改成「路过出生点交 500」，居然真有人信了</t>
+          <t>你在曼谷把大富翁说明书改成「路过出生点交 500」，全团居然信了</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>v5 邪恶版</t>
+          <t>v6 邪恶版</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>你贿赂骰子之神</t>
+          <t>你在拉斯维加斯贿赂了骰子之神</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>v5 邪恶版</t>
+          <t>v6 邪恶版</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>你出千被真正的赌场抓了现行</t>
+          <t>你在拉斯维加斯出千被真正的赌场抓了现行</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>强制拍卖该处房子，拍卖所得上交银行（你一分拿不到）</t>
+          <t>强制拍卖该处房子，拍卖所得上交赌场（你一分拿不到）</t>
         </is>
       </c>
       <c r="G36" s="2" t="n"/>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>v5 邪恶版</t>
+          <t>v6 邪恶版</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>你造的假币被人用回你自己的店</t>
+          <t>你在平壤造的假美元被人用回你自己的黑市摊位</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>v5 邪恶版</t>
+          <t>v6 邪恶版</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>你买的「纯金」纪念币是镀金的</t>
+          <t>你在开罗买的「图坦卡蒙纯金」圣甲虫是镀金的</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>v5 邪恶版</t>
+          <t>v6 邪恶版</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>你教唆的小孩把他家房契拿去换卡牌，家长找上门</t>
+          <t>你在那不勒斯教唆小孩把家里房契拿去换球星卡，黑手党家长找上门</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>v5 邪恶版</t>
+          <t>v6 邪恶版</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>你的诈骗集团被一锅端，你是唯一没跑掉的</t>
+          <t>你在哥伦比亚的诈骗集团被一锅端，你是唯一没跑掉的</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>v5 邪恶版</t>
+          <t>v6 邪恶版</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>你被全网曝光，人肉搜索出所有黑历史</t>
+          <t>你在首尔被全网人肉，黑历史挂上热搜</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -1688,7 +1688,7 @@
   <autoFilter ref="A1:G41"/>
   <conditionalFormatting sqref="B2:B41">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
-      <formula>"v5 邪恶版"</formula>
+      <formula>"v6 邪恶版"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1705,7 +1705,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>v5 邪恶版</t>
+          <t>v6 邪恶版</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>魔鬼跟你玩「灵魂赌局」：他背对背走十六步才回头索命——你押他会在前八步还是后八步回头</t>
+          <t>你在德州跟亡命牛仔玩「灵魂赌局」：背对背各走十六步才回头开枪——你押他会在前八步还是后八步回头</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>抢先点名魔鬼真名，他倒赔封口费：+3000</t>
+          <t>抢先点名牛仔真名，他倒赔封口费：+3000</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>v5 邪恶版</t>
+          <t>v6 邪恶版</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>地下钱庄最后一注，庄家冷笑：单还是双</t>
+          <t>你在澳门地下钱庄押上最后一注，庄家冷笑：单还是双</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>v5 邪恶版</t>
+          <t>v6 邪恶版</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>你和左手玩家各自雇了杀手互杀——谁先得手，就看各自杀手的骰点</t>
+          <t>你和左手玩家在西西里各自雇了杀手互杀——谁先得手，就看各自杀手的骰点</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>v5 邪恶版</t>
+          <t>v6 邪恶版</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>亡命狂奔：宪兵队放狗追你——你跑出的步数 = 这回合的移动骰点数，9 步以上才能翻墙</t>
+          <t>亡命狂奔：马德里宪兵队放狗追你——你跑出的步数 = 这回合的移动骰点数，9 步以上才能翻墙</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>v5 邪恶版</t>
+          <t>v6 邪恶版</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>巫婆把诅咒骰攥在拳头里让你猜——猜错就中咒</t>
+          <t>你在河内老街碰上巫祝：她把诅咒骰攥在拳头里让你猜在哪只手——猜错就中咒</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>v5 邪恶版</t>
+          <t>v6 邪恶版</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>黑帮谈判破裂，双方按江湖规矩一局手势定生死</t>
+          <t>你在那不勒斯和黑手党谈判破裂，双方按江湖规矩一局手势定生死</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>v5 邪恶版</t>
+          <t>v6 邪恶版</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -2746,17 +2746,17 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>你潜入魔王的火山老巢，卫兵报告警戒等级 1-16，1-7 级可以摸进宝库</t>
+          <t>你潜入西西里黑手党的金库，守卫报告警戒等级 1-16，1-7 级可以摸进宝库</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>偷出魔物蛋卖给收藏家：+900</t>
+          <t>偷出教父的藏品卖给收藏家：+900</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>触发警报被熔岩燎到：-700</t>
+          <t>触发警报被探照灯燎到：-700</t>
         </is>
       </c>
       <c r="I28" s="2" t="n"/>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>v5 邪恶版</t>
+          <t>v6 邪恶版</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
@@ -2783,17 +2783,17 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>死神的轮盘：十六格命盘，14、15、16 三格写着「缓刑」，其余都是「即刻带走」</t>
+          <t>你在蒙特卡洛把全部身家压上轮盘：十六格轮盘里 14、15、16 三格是「连本带利」，其余全吞</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>死神输了面子，倒赔你阳寿钱：+2600</t>
+          <t>连本带利：+2600</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>交赎命钱：-600</t>
+          <t>全被吞掉：-600</t>
         </is>
       </c>
       <c r="I29" s="2" t="n"/>
@@ -2804,7 +2804,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>v5 邪恶版</t>
+          <t>v6 邪恶版</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>你跟食人族跳完祭祀舞，族长掷命运骨：只有掷出 1 的人会成为今晚的主菜</t>
+          <t>你在巴布亚新几内亚跟部落跳完祭祀舞，族长掷命运骨：只有掷出 1 的人会成为今晚的主菜</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>v5 邪恶版</t>
+          <t>v6 邪恶版</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>歌舞厅老板娘逼你竞猜她给你打的「好感分」（3-14 分，差 2 以内她请你喝酒）</t>
+          <t>你在巴黎红磨坊即兴演出，老板娘逼你竞猜她给你打的「好感分」（3-14 分，差 2 以内她请你喝酒）</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>-1000（她男人的医药费归你出）</t>
+          <t>-1000（她相好的医药费归你出）</t>
         </is>
       </c>
       <c r="I31" s="2" t="n"/>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>v5 邪恶版</t>
+          <t>v6 邪恶版</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
@@ -2894,17 +2894,17 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>你对恶魔撒了个弥天大谎。恶魔的测谎仪是颗十六面骰：单数=通过，双数=识破</t>
+          <t>你在缅甸对军阀撒了个弥天大谎。军阀的测谎仪是颗十六面骰：单数=通过，双数=识破</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>谎言生效，恶魔信了还倒贴「诚意金」：+800</t>
+          <t>谎言生效，军阀信了还倒贴「诚意金」：+800</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>被识破，舌头被施咒：下回合禁止交易与谈判</t>
+          <t>被识破，被押去跪榴莲：下回合禁止交易与谈判</t>
         </is>
       </c>
       <c r="I32" s="2" t="n"/>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>v5 邪恶版</t>
+          <t>v6 邪恶版</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>你潜入首富卧室行窃，惊醒了他——床上床下各显身手</t>
+          <t>你潜入苏黎世首富的卧室行窃，惊醒了他——床上床下各显身手</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>v5 邪恶版</t>
+          <t>v6 邪恶版</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>你去抢恶魔银行。地狱金库门是 1-16 密码转盘，恶魔守卫今天设的是小户门还是大户门全看运气</t>
+          <t>你去抢瑞士银行。金库大门是 1-16 密码转盘，守卫今天设的是小户门还是大户门全看运气</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>传入地狱监狱：坐牢 3 回合</t>
+          <t>被押进瑞士监狱：坐牢 3 回合</t>
         </is>
       </c>
       <c r="I34" s="2" t="n"/>
@@ -2989,7 +2989,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>v5 邪恶版</t>
+          <t>v6 邪恶版</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
@@ -3005,17 +3005,17 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>巨龙喝醉了朝你最高的塔楼俯冲——风力 9 级以上才能让它拉起机头</t>
+          <t>台风「醉汉」朝你名下等级最高的那栋楼拐来——风力 9 级以上它才拐得走</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>巨龙擦着塔尖拉起，还赔钱帮你加盖：那栋房 +1 级</t>
+          <t>台风擦楼而过，保险公司赔钱帮你加盖：那栋房 +1 级</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>撞烂塔顶：那栋房 -1 级（1 级 → 空地；无房则 ±1000）</t>
+          <t>撞烂楼顶：那栋房 -1 级（1 级 → 空地；无房则 ±1000）</t>
         </is>
       </c>
       <c r="I35" s="2" t="n"/>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>v5 邪恶版</t>
+          <t>v6 邪恶版</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
@@ -3042,17 +3042,17 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>魔王税务局搞单双号抽魂：单号格退魂给钱，双号格抽魂给钱，数额 = 骰点 × 100</t>
+          <t>伦敦税务局搞路段单双号抽查：单号格退税、双号格补税，税额 = 骰点 × 100</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>退魂费：+点数 × 100（均值 +850）</t>
+          <t>退税：+点数 × 100（均值 +850）</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>抽魂费：-点数 × 100（均值 -850）</t>
+          <t>补税：-点数 × 100（均值 -850）</t>
         </is>
       </c>
       <c r="I36" s="2" t="n"/>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>v5 邪恶版</t>
+          <t>v6 邪恶版</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>双头恶魔要吃地契：它嘴里有两杆秤，1-8 吃你的、9-16 吃左手的</t>
+          <t>东西两大财团要在你和左手玩家的地盘上建总部，董事会转盘 1-8 买你的地、9-16 买他的地——被买走的地归赢家</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>吃掉左手玩家购地款最低的一块地（归你）</t>
+          <t>财团买走左手玩家购地款最低的一块地（归你）</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>吃掉你的那块（归他）</t>
+          <t>买走你的那块（归他）</t>
         </is>
       </c>
       <c r="I37" s="2" t="n"/>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>v5 邪恶版</t>
+          <t>v6 邪恶版</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>传送门故障，奇偶决定把你扔向未来还是过去</t>
+          <t>你掉进百慕大三角，奇偶决定把你扔向未来还是过去</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>v5 邪恶版</t>
+          <t>v6 邪恶版</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>赏金猎人放出的悬赏令同时锁定了你和顺时针最近的玩家——赏金归活下来的那个</t>
+          <t>索马里海岸，赏金猎人放出的通缉令同时锁定了你和顺时针最近的玩家——赏金归活下来的那个</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>v5 邪恶版</t>
+          <t>v6 邪恶版</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
@@ -3190,17 +3190,17 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>你向魔王告发了自己的黑帮兄弟——赏金必拿，牢也必坐，魔王掷骰决定关你多久</t>
+          <t>你向国际刑警告发了同船的蛇头——赏金必拿，证人保护也必进，法官掷骰决定关你多久</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>魔王高兴：关 1 回合，净 +1000</t>
+          <t>法官心情好：关 1 回合，净 +1000</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>魔王嫌弃告密者：关 3 回合，净 -1000</t>
+          <t>法官心情差：关 3 回合，净 -1000</t>
         </is>
       </c>
       <c r="I40" s="2" t="n"/>
@@ -3211,7 +3211,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>v5 邪恶版</t>
+          <t>v6 邪恶版</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>黑市「决斗拍卖」：你和右手玩家各押一块购地款最低的地，中间人（右手玩家的下家）掷骰定谁先喊价，≥9 你先</t>
+          <t>迪拜黑市「决斗拍卖」：你和右手玩家各押一块购地款最低的地，中间人（右手玩家的下家）掷骰定谁先喊价，≥9 你先</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -3246,7 +3246,7 @@
   <autoFilter ref="A1:I41"/>
   <conditionalFormatting sqref="B2:B41">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
-      <formula>"v5 邪恶版"</formula>
+      <formula>"v6 邪恶版"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/机会命运卡牌总表.xlsx
+++ b/机会命运卡牌总表.xlsx
@@ -2608,7 +2608,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>你进了医院：-2000</t>
+          <t>你重伤治疗：-2000（医药费）</t>
         </is>
       </c>
       <c r="I24" s="2" t="n"/>
